--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.46964340055094</v>
+        <v>6.413817052589527</v>
       </c>
       <c r="D2" t="n">
-        <v>39.49761867862394</v>
+        <v>6.41836303527639</v>
       </c>
       <c r="E2" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F2" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.75944410519813</v>
+        <v>7.273409667094696</v>
       </c>
       <c r="D3" t="n">
-        <v>45.67548576643712</v>
+        <v>7.422266437046032</v>
       </c>
       <c r="E3" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F3" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.543007033372048</v>
+        <v>1.550738642922958</v>
       </c>
       <c r="D4" t="n">
-        <v>9.422545204072492</v>
+        <v>1.53116359566178</v>
       </c>
       <c r="E4" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F4" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.90022726167202</v>
+        <v>6.646286930021704</v>
       </c>
       <c r="D5" t="n">
-        <v>37.03190357942797</v>
+        <v>6.017684331657045</v>
       </c>
       <c r="E5" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F5" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.14527658504196</v>
+        <v>7.498607445069319</v>
       </c>
       <c r="D6" t="n">
-        <v>28.62254356272342</v>
+        <v>4.651163328942556</v>
       </c>
       <c r="E6" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F6" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.4050716352303</v>
+        <v>4.290824140724923</v>
       </c>
       <c r="D7" t="n">
-        <v>30.82573035966099</v>
+        <v>5.009181183444912</v>
       </c>
       <c r="E7" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F7" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.74346214578962</v>
+        <v>7.758312598690813</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87718774772754</v>
+        <v>5.017543009005725</v>
       </c>
       <c r="E8" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F8" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.04136888048344</v>
+        <v>4.719222443078558</v>
       </c>
       <c r="D9" t="n">
-        <v>31.03378594559146</v>
+        <v>5.042990216158613</v>
       </c>
       <c r="E9" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F9" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.43204448479901</v>
+        <v>4.13270722877984</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48469043402062</v>
+        <v>3.816262195528351</v>
       </c>
       <c r="E10" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F10" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.14920509187632</v>
+        <v>4.411745827429902</v>
       </c>
       <c r="D11" t="n">
-        <v>23.32181515361401</v>
+        <v>3.789794962462277</v>
       </c>
       <c r="E11" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F11" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.79808908478821</v>
+        <v>4.517189476278085</v>
       </c>
       <c r="D12" t="n">
-        <v>25.70029095906602</v>
+        <v>4.176297280848229</v>
       </c>
       <c r="E12" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F12" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.55697050259492</v>
+        <v>2.203007706671674</v>
       </c>
       <c r="D13" t="n">
-        <v>42.38349089622957</v>
+        <v>6.887317270637305</v>
       </c>
       <c r="E13" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F13" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>58.46874316333225</v>
+        <v>9.501170764041492</v>
       </c>
       <c r="D14" t="n">
-        <v>56.28187594095026</v>
+        <v>9.145804840404416</v>
       </c>
       <c r="E14" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F14" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.90570042768941</v>
+        <v>2.25967631949953</v>
       </c>
       <c r="D15" t="n">
-        <v>53.13266059650724</v>
+        <v>8.634057346932426</v>
       </c>
       <c r="E15" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F15" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>42.13594915133149</v>
+        <v>6.847091737091368</v>
       </c>
       <c r="D16" t="n">
-        <v>50.57825552810322</v>
+        <v>8.218966523316773</v>
       </c>
       <c r="E16" t="n">
-        <v>13.74771837646163</v>
+        <v>2.234004236175015</v>
       </c>
       <c r="F16" t="n">
-        <v>12.42894948259058</v>
+        <v>2.01970429092097</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
